--- a/data/gold/results/scenarios/zorg_en_welzijn/full_results_tables.xlsx
+++ b/data/gold/results/scenarios/zorg_en_welzijn/full_results_tables.xlsx
@@ -462,19 +462,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>251.4213558693373</v>
+        <v>539.3898178684632</v>
       </c>
       <c r="C2">
-        <v>256.7440191262457</v>
+        <v>174.0255185453556</v>
       </c>
       <c r="D2">
-        <v>8.100586546573025</v>
+        <v>24.95066712284193</v>
       </c>
       <c r="E2">
-        <v>722.8627504106237</v>
+        <v>1965.00904738581</v>
       </c>
       <c r="F2">
-        <v>111.9217889127454</v>
+        <v>42.13390835671613</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -482,19 +482,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>254.6703648544448</v>
+        <v>92.19443138066937</v>
       </c>
       <c r="C3">
-        <v>17.86268760895015</v>
+        <v>37.71808415051622</v>
       </c>
       <c r="D3">
-        <v>0.241918554494725</v>
+        <v>0.3600299707192465</v>
       </c>
       <c r="E3">
-        <v>8.380026854362468</v>
+        <v>18.33879821675272</v>
       </c>
       <c r="F3">
-        <v>11.63891589201688</v>
+        <v>0.9111748581760284</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -502,7 +502,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>606.2380000000001</v>
+        <v>627.294307534464</v>
       </c>
       <c r="C4">
         <v>27.5319</v>
@@ -522,19 +522,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>937.0204881134468</v>
+        <v>211.0271906274781</v>
       </c>
       <c r="C5">
-        <v>819.3521534767875</v>
+        <v>187.5553578002819</v>
       </c>
       <c r="D5">
-        <v>6.693409162660959</v>
+        <v>2.746923736623413</v>
       </c>
       <c r="E5">
-        <v>540.878436905356</v>
+        <v>137.5442023659014</v>
       </c>
       <c r="F5">
-        <v>238.1270399184256</v>
+        <v>8.346162094683887</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -542,7 +542,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>142.1847557754865</v>
+        <v>131.0762816237094</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -554,7 +554,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>45.1</v>
+        <v>42.75704592555413</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -562,19 +562,19 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>1694.790010672312</v>
+        <v>1807.500111998285</v>
       </c>
       <c r="C7">
-        <v>3596.577638504079</v>
+        <v>2280.72844895429</v>
       </c>
       <c r="D7">
-        <v>24.74405594203506</v>
+        <v>58.51576406926836</v>
       </c>
       <c r="E7">
-        <v>2023.586694223467</v>
+        <v>2115.250269276848</v>
       </c>
       <c r="F7">
-        <v>852.9827281901071</v>
+        <v>102.2546830106221</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -582,19 +582,19 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>374.031549283389</v>
+        <v>768.8461173311747</v>
       </c>
       <c r="C8">
-        <v>375.1765079937036</v>
+        <v>454.0327903713752</v>
       </c>
       <c r="D8">
-        <v>3.831377786335066</v>
+        <v>13.30315303454863</v>
       </c>
       <c r="E8">
-        <v>391.0034419357486</v>
+        <v>860.6529145935858</v>
       </c>
       <c r="F8">
-        <v>86.39920737536336</v>
+        <v>36.87757225302859</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -602,19 +602,19 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>426.2236926679274</v>
+        <v>740.4325251824581</v>
       </c>
       <c r="C9">
-        <v>207.6325422231732</v>
+        <v>162.6854972800678</v>
       </c>
       <c r="D9">
-        <v>0.9618793994927206</v>
+        <v>3.13275206868769</v>
       </c>
       <c r="E9">
-        <v>107.1134256622356</v>
+        <v>224.823404360135</v>
       </c>
       <c r="F9">
-        <v>23.0249984090125</v>
+        <v>10.61685691935037</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -622,19 +622,19 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>638.3130524849985</v>
+        <v>364.5930035415449</v>
       </c>
       <c r="C10">
-        <v>746.1586785537951</v>
+        <v>1488.850117685972</v>
       </c>
       <c r="D10">
-        <v>2.194736891773225</v>
+        <v>2.941000522442835</v>
       </c>
       <c r="E10">
-        <v>438.8551798278893</v>
+        <v>258.0024555214974</v>
       </c>
       <c r="F10">
-        <v>235.2672169618324</v>
+        <v>44.70587095599213</v>
       </c>
     </row>
   </sheetData>
@@ -672,19 +672,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>4.721622446387446</v>
+        <v>10.21116418190132</v>
       </c>
       <c r="C2">
-        <v>4.24578278868252</v>
+        <v>3.61564306741081</v>
       </c>
       <c r="D2">
-        <v>17.25031507802563</v>
+        <v>23.50700984733578</v>
       </c>
       <c r="E2">
-        <v>17.07090493617585</v>
+        <v>35.20629765740712</v>
       </c>
       <c r="F2">
-        <v>6.975658893210465</v>
+        <v>14.59924820606745</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -692,19 +692,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>4.782637922577028</v>
+        <v>1.745328599648548</v>
       </c>
       <c r="C3">
-        <v>0.2953957481377614</v>
+        <v>0.7836501831154643</v>
       </c>
       <c r="D3">
-        <v>0.5151690268675657</v>
+        <v>0.3391984681357635</v>
       </c>
       <c r="E3">
-        <v>0.1979001431629447</v>
+        <v>0.3285690666702351</v>
       </c>
       <c r="F3">
-        <v>0.7254093053567211</v>
+        <v>0.315718822023776</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -712,16 +712,16 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>11.3849793656376</v>
+        <v>11.8752800894891</v>
       </c>
       <c r="C4">
-        <v>0.4552957749806399</v>
+        <v>0.5720168179915724</v>
       </c>
       <c r="D4">
-        <v>0.4069501871818537</v>
+        <v>0.1800428645738831</v>
       </c>
       <c r="E4">
-        <v>0.04232876848367189</v>
+        <v>0.03211372894444833</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -732,19 +732,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>17.59698158536955</v>
+        <v>3.994946176140183</v>
       </c>
       <c r="C5">
-        <v>13.54964872381747</v>
+        <v>3.896745918959029</v>
       </c>
       <c r="D5">
-        <v>14.25371068356678</v>
+        <v>2.587985443786887</v>
       </c>
       <c r="E5">
-        <v>12.7732192220359</v>
+        <v>2.464325615185732</v>
       </c>
       <c r="F5">
-        <v>14.84155158577606</v>
+        <v>2.891915246902069</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -752,7 +752,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2.670189777962014</v>
+        <v>2.481399143391371</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>2.810911254546307</v>
+        <v>14.81516313987732</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -772,19 +772,19 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>31.82768038393006</v>
+        <v>34.21770265400227</v>
       </c>
       <c r="C7">
-        <v>59.47670168788767</v>
+        <v>47.38557927617373</v>
       </c>
       <c r="D7">
-        <v>52.69282154499962</v>
+        <v>55.13001457750172</v>
       </c>
       <c r="E7">
-        <v>47.78840252534258</v>
+        <v>37.89811079961393</v>
       </c>
       <c r="F7">
-        <v>53.16316520184446</v>
+        <v>35.43088110568937</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -792,19 +792,19 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>7.02420744111858</v>
+        <v>14.55499098168092</v>
       </c>
       <c r="C8">
-        <v>6.204304060436203</v>
+        <v>9.433217177603751</v>
       </c>
       <c r="D8">
-        <v>8.158973873958406</v>
+        <v>12.53342637469849</v>
       </c>
       <c r="E8">
-        <v>9.233817323151721</v>
+        <v>15.41998126227842</v>
       </c>
       <c r="F8">
-        <v>5.384933578609515</v>
+        <v>12.7779465887914</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -812,19 +812,19 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>8.004361234647474</v>
+        <v>14.01709455720877</v>
       </c>
       <c r="C9">
-        <v>3.433624966773092</v>
+        <v>3.380036992997976</v>
       </c>
       <c r="D9">
-        <v>2.048335958503044</v>
+        <v>2.951489568007796</v>
       </c>
       <c r="E9">
-        <v>2.529557797561799</v>
+        <v>4.028072901132267</v>
       </c>
       <c r="F9">
-        <v>1.435060469263948</v>
+        <v>3.67870286377537</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -832,19 +832,19 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>11.98733984237025</v>
+        <v>6.902093616537502</v>
       </c>
       <c r="C10">
-        <v>12.33924624928466</v>
+        <v>30.93311056574766</v>
       </c>
       <c r="D10">
-        <v>4.67372364689709</v>
+        <v>2.77083285595968</v>
       </c>
       <c r="E10">
-        <v>10.36386928408554</v>
+        <v>4.622528968767827</v>
       </c>
       <c r="F10">
-        <v>14.66330971139252</v>
+        <v>15.49042402687325</v>
       </c>
     </row>
   </sheetData>
@@ -882,19 +882,19 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>356.3909715309685</v>
+        <v>706.5277153933312</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>54.88861254250904</v>
       </c>
       <c r="D2">
-        <v>35.99768281500528</v>
+        <v>90.4110443436922</v>
       </c>
       <c r="E2">
-        <v>3954.319015637903</v>
+        <v>5520.277479487429</v>
       </c>
       <c r="F2">
-        <v>182.9900208566815</v>
+        <v>57.35197527105783</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -902,19 +902,19 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>1439.097049907746</v>
+        <v>486.3533896077828</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>10.70584032157804</v>
       </c>
       <c r="D3">
-        <v>2.524095842883239</v>
+        <v>4.210687091905415</v>
       </c>
       <c r="E3">
-        <v>1.661750468928396E-05</v>
+        <v>2.447213312740727</v>
       </c>
       <c r="F3">
-        <v>42.32886562674162</v>
+        <v>16.10924672816802</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -922,19 +922,19 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>488.5762909571955</v>
+        <v>815.7451939802019</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>20.50891629999609</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.07402543737522105</v>
       </c>
       <c r="E4">
-        <v>14.71203874219202</v>
+        <v>2.013140500209978</v>
       </c>
       <c r="F4">
-        <v>11.75633503502459</v>
+        <v>14.86302268282213</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -942,19 +942,19 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>1.314348172154342</v>
+        <v>132.5774026436177</v>
       </c>
       <c r="C5">
-        <v>6019.50422748673</v>
+        <v>4096.53153887731</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.03927630077308847</v>
       </c>
       <c r="E5">
-        <v>0.05249999170978694</v>
+        <v>0.5840111205736365</v>
       </c>
       <c r="F5">
-        <v>937.8189572836507</v>
+        <v>0.3557056837071935</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -962,7 +962,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>142.1847557754865</v>
+        <v>131.0762816237094</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>45.1</v>
+        <v>42.75704592555413</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -982,19 +982,19 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>353.8804600177943</v>
+        <v>475.9604465993463</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>341.7127120929816</v>
       </c>
       <c r="D7">
-        <v>3.725858377936198</v>
+        <v>7.921516635667841</v>
       </c>
       <c r="E7">
-        <v>9.249808037470167</v>
+        <v>0.8286741409179013</v>
       </c>
       <c r="F7">
-        <v>99.34483299496961</v>
+        <v>69.51592016021064</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1002,19 +1002,19 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>578.0831935686183</v>
+        <v>874.1442957579286</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>26.94813147887068</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.04153941800077849</v>
       </c>
       <c r="E8">
-        <v>64.42650678658809</v>
+        <v>5.394600809907912</v>
       </c>
       <c r="F8">
-        <v>2.112003912704452</v>
+        <v>2.908883245275701</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1022,19 +1022,19 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>1965.366199791377</v>
+        <v>1659.969061482331</v>
       </c>
       <c r="C9">
-        <v>27.5319</v>
+        <v>261.8319631746158</v>
       </c>
       <c r="D9">
-        <v>4.71142724754008</v>
+        <v>3.443301297717567</v>
       </c>
       <c r="E9">
-        <v>191.7124700063158</v>
+        <v>49.86837234875181</v>
       </c>
       <c r="F9">
-        <v>283.010879949732</v>
+        <v>84.74147467732816</v>
       </c>
     </row>
   </sheetData>
@@ -1072,19 +1072,19 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>6.692922345645793</v>
+        <v>13.37524414060091</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1.140393851878669</v>
       </c>
       <c r="D2">
-        <v>76.65758116001776</v>
+        <v>85.17981900970545</v>
       </c>
       <c r="E2">
-        <v>93.38398467056352</v>
+        <v>98.90465000803484</v>
       </c>
       <c r="F2">
-        <v>11.4050711551155</v>
+        <v>19.87225383891903</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1092,19 +1092,19 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>27.02583839737798</v>
+        <v>9.207133963586177</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.2224300071798511</v>
       </c>
       <c r="D3">
-        <v>5.37509825079159</v>
+        <v>3.967054766357532</v>
       </c>
       <c r="E3">
-        <v>3.924338924174473E-07</v>
+        <v>0.04384576266157171</v>
       </c>
       <c r="F3">
-        <v>2.638197001826746</v>
+        <v>5.581796243685438</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1112,19 +1112,19 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>9.175325517515272</v>
+        <v>15.44283527495152</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.4261037212244434</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.0697422909281496</v>
       </c>
       <c r="E4">
-        <v>0.3474349932163899</v>
+        <v>0.03606865005067748</v>
       </c>
       <c r="F4">
-        <v>0.7327275933961782</v>
+        <v>5.149984079374933</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1132,19 +1132,19 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>0.02468308951144712</v>
+        <v>2.509816797346649</v>
       </c>
       <c r="C5">
-        <v>99.54470422501936</v>
+        <v>85.1116318042241</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.03700375563083343</v>
       </c>
       <c r="E5">
-        <v>0.001239823696986311</v>
+        <v>0.01046349856429663</v>
       </c>
       <c r="F5">
-        <v>58.45068429613068</v>
+        <v>0.1232507442885361</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1152,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2.670189777962014</v>
+        <v>2.48139914339137</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>2.810911254546304</v>
+        <v>14.8151631398773</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1172,19 +1172,19 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>6.645775644556974</v>
+        <v>9.010385630791047</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>7.099597856983993</v>
       </c>
       <c r="D7">
-        <v>7.9342687823873</v>
+        <v>7.463173976218247</v>
       </c>
       <c r="E7">
-        <v>0.2184406287304631</v>
+        <v>0.01484703009635742</v>
       </c>
       <c r="F7">
-        <v>6.1917851252014</v>
+        <v>24.0870171383071</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1192,19 +1192,19 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>10.85624000871045</v>
+        <v>16.54838602243218</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.5598881450013304</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.03913592783669327</v>
       </c>
       <c r="E8">
-        <v>1.521476617931936</v>
+        <v>0.09665295033077663</v>
       </c>
       <c r="F8">
-        <v>0.1316331611500393</v>
+        <v>1.007917616868353</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1212,19 +1212,19 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>36.90902521872007</v>
+        <v>31.42479902690015</v>
       </c>
       <c r="C9">
-        <v>0.4552957749806402</v>
+        <v>5.439954613507614</v>
       </c>
       <c r="D9">
-        <v>10.03305180680335</v>
+        <v>3.244070273323076</v>
       </c>
       <c r="E9">
-        <v>4.527422873426819</v>
+        <v>0.8934721002614577</v>
       </c>
       <c r="F9">
-        <v>17.63899041263314</v>
+        <v>29.36261719867933</v>
       </c>
     </row>
   </sheetData>
@@ -1262,7 +1262,7 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>246.6378</v>
+        <v>255.2290121415143</v>
       </c>
       <c r="C2">
         <v>27.5319</v>
@@ -1282,19 +1282,19 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>430.0978191319215</v>
+        <v>367.5623030801248</v>
       </c>
       <c r="C3">
-        <v>412.2758078554427</v>
+        <v>339.29452653595</v>
       </c>
       <c r="D3">
-        <v>6.260941706597694</v>
+        <v>28.807418501821</v>
       </c>
       <c r="E3">
-        <v>131.2900800734625</v>
+        <v>296.5294847474988</v>
       </c>
       <c r="F3">
-        <v>11.60108931449432</v>
+        <v>3.230907999678469</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1302,19 +1302,19 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>738.578748993355</v>
+        <v>1751.633462026786</v>
       </c>
       <c r="C4">
-        <v>600.5306809163937</v>
+        <v>1060.439760104241</v>
       </c>
       <c r="D4">
-        <v>4.740319192884074</v>
+        <v>14.28202951421271</v>
       </c>
       <c r="E4">
-        <v>1124.950940019148</v>
+        <v>1817.199551324957</v>
       </c>
       <c r="F4">
-        <v>155.3463637422545</v>
+        <v>81.67064086590919</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1322,19 +1322,19 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>2049.015657251864</v>
+        <v>964.0859558803688</v>
       </c>
       <c r="C5">
-        <v>2798.207721613609</v>
+        <v>861.5021612636117</v>
       </c>
       <c r="D5">
-        <v>25.15880944593383</v>
+        <v>44.65201362135661</v>
       </c>
       <c r="E5">
-        <v>953.9605285404436</v>
+        <v>1262.462612444656</v>
       </c>
       <c r="F5">
-        <v>433.0767337885352</v>
+        <v>32.84276627361291</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1342,19 +1342,19 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>307.8047259770235</v>
+        <v>337.5221815362431</v>
       </c>
       <c r="C6">
-        <v>1667.122285842542</v>
+        <v>179.1545276473159</v>
       </c>
       <c r="D6">
-        <v>7.009746438629683</v>
+        <v>7.771501418626241</v>
       </c>
       <c r="E6">
-        <v>1175.789267473257</v>
+        <v>612.6302849528141</v>
       </c>
       <c r="F6">
-        <v>666.3023675634898</v>
+        <v>10.82640627800862</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1362,19 +1362,19 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>99.30809651793798</v>
+        <v>223.6275001589907</v>
       </c>
       <c r="C7">
-        <v>93.92992416496551</v>
+        <v>106.0920220748683</v>
       </c>
       <c r="D7">
-        <v>2.567509503035408</v>
+        <v>5.151620760690903</v>
       </c>
       <c r="E7">
-        <v>625.8939995106476</v>
+        <v>1127.444539539013</v>
       </c>
       <c r="F7">
-        <v>53.77459411807701</v>
+        <v>17.1070210157356</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1382,19 +1382,19 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>1453.450421849239</v>
+        <v>1382.693372264221</v>
       </c>
       <c r="C8">
-        <v>447.4378070937803</v>
+        <v>2239.112817161874</v>
       </c>
       <c r="D8">
-        <v>1.03063799628409</v>
+        <v>5.285706708424679</v>
       </c>
       <c r="E8">
-        <v>220.7951402027215</v>
+        <v>463.3546187115919</v>
       </c>
       <c r="F8">
-        <v>284.3607471326532</v>
+        <v>142.9255319411789</v>
       </c>
     </row>
   </sheetData>
@@ -1432,16 +1432,16 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>4.63178861072096</v>
+        <v>4.831728854764994</v>
       </c>
       <c r="C2">
-        <v>0.45529577498064</v>
+        <v>0.5720168179915723</v>
       </c>
       <c r="D2">
-        <v>0.4069501871818537</v>
+        <v>0.180042864573883</v>
       </c>
       <c r="E2">
-        <v>0.0423287684836719</v>
+        <v>0.03211372894444833</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1452,19 +1452,19 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>8.077116241513496</v>
+        <v>6.958305291451017</v>
       </c>
       <c r="C3">
-        <v>6.817816185708694</v>
+        <v>7.049356398615831</v>
       </c>
       <c r="D3">
-        <v>13.3327650415207</v>
+        <v>27.14060778674271</v>
       </c>
       <c r="E3">
-        <v>3.100506250631746</v>
+        <v>5.312802665263391</v>
       </c>
       <c r="F3">
-        <v>0.7230517188272496</v>
+        <v>1.119498039890622</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1472,19 +1472,19 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>13.87030146112216</v>
+        <v>33.16009363682408</v>
       </c>
       <c r="C4">
-        <v>9.930992113420466</v>
+        <v>22.03223813999666</v>
       </c>
       <c r="D4">
-        <v>10.09457761824127</v>
+        <v>13.45566460317948</v>
       </c>
       <c r="E4">
-        <v>26.56649625951775</v>
+        <v>32.5580527947014</v>
       </c>
       <c r="F4">
-        <v>9.682147277072003</v>
+        <v>28.29858429119465</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1492,19 +1492,19 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>38.47993853516412</v>
+        <v>18.25106751154952</v>
       </c>
       <c r="C5">
-        <v>46.274036778024</v>
+        <v>17.89900896701185</v>
       </c>
       <c r="D5">
-        <v>53.57604507218924</v>
+        <v>42.0684272181114</v>
       </c>
       <c r="E5">
-        <v>22.52843916265885</v>
+        <v>22.61904828082336</v>
       </c>
       <c r="F5">
-        <v>26.99202361614962</v>
+        <v>11.37990078069523</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1512,19 +1512,19 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>5.780486300585164</v>
+        <v>6.389617112758607</v>
       </c>
       <c r="C6">
-        <v>27.56924633316901</v>
+        <v>3.722205980466326</v>
       </c>
       <c r="D6">
-        <v>14.9273554437346</v>
+        <v>7.321838709834978</v>
       </c>
       <c r="E6">
-        <v>27.76707860324798</v>
+        <v>10.97625692598461</v>
       </c>
       <c r="F6">
-        <v>41.52808922206347</v>
+        <v>3.751310965368355</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1532,19 +1532,19 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>1.864978159893426</v>
+        <v>4.233482064484347</v>
       </c>
       <c r="C7">
-        <v>1.553321696525148</v>
+        <v>2.204222043577008</v>
       </c>
       <c r="D7">
-        <v>5.467548261912336</v>
+        <v>4.853545572752886</v>
       </c>
       <c r="E7">
-        <v>14.78092066536803</v>
+        <v>20.19998233801284</v>
       </c>
       <c r="F7">
-        <v>3.351565672176546</v>
+        <v>5.927521457556067</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1552,19 +1552,19 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>27.29539069100065</v>
+        <v>26.17570552816744</v>
       </c>
       <c r="C8">
-        <v>7.399291118172041</v>
+        <v>46.52095165234075</v>
       </c>
       <c r="D8">
-        <v>2.194758375219995</v>
+        <v>4.979873244804656</v>
       </c>
       <c r="E8">
-        <v>5.214230290091987</v>
+        <v>8.301743266269957</v>
       </c>
       <c r="F8">
-        <v>17.72312249371111</v>
+        <v>49.52318446529506</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/scenarios/zorg_en_welzijn/full_results_tables.xlsx
+++ b/data/gold/results/scenarios/zorg_en_welzijn/full_results_tables.xlsx
@@ -505,13 +505,13 @@
         <v>627.294307534464</v>
       </c>
       <c r="C4">
-        <v>27.5319</v>
+        <v>25.6351</v>
       </c>
       <c r="D4">
-        <v>0.1911</v>
+        <v>0.1776</v>
       </c>
       <c r="E4">
-        <v>1.7924</v>
+        <v>1.6692</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -675,13 +675,13 @@
         <v>10.21116418190132</v>
       </c>
       <c r="C2">
-        <v>3.61564306741081</v>
+        <v>3.617068513807321</v>
       </c>
       <c r="D2">
-        <v>23.50700984733578</v>
+        <v>23.5100000568968</v>
       </c>
       <c r="E2">
-        <v>35.20629765740712</v>
+        <v>35.20707479237855</v>
       </c>
       <c r="F2">
         <v>14.59924820606745</v>
@@ -695,13 +695,13 @@
         <v>1.745328599648548</v>
       </c>
       <c r="C3">
-        <v>0.7836501831154643</v>
+        <v>0.7839591326740409</v>
       </c>
       <c r="D3">
-        <v>0.3391984681357635</v>
+        <v>0.3392416158822906</v>
       </c>
       <c r="E3">
-        <v>0.3285690666702351</v>
+        <v>0.3285763194212833</v>
       </c>
       <c r="F3">
         <v>0.315718822023776</v>
@@ -715,13 +715,13 @@
         <v>11.8752800894891</v>
       </c>
       <c r="C4">
-        <v>0.5720168179915724</v>
+        <v>0.5328179098867951</v>
       </c>
       <c r="D4">
-        <v>0.1800428645738831</v>
+        <v>0.1673452653409168</v>
       </c>
       <c r="E4">
-        <v>0.03211372894444833</v>
+        <v>0.02990706293267251</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -735,13 +735,13 @@
         <v>3.994946176140183</v>
       </c>
       <c r="C5">
-        <v>3.896745918959029</v>
+        <v>3.898282188531202</v>
       </c>
       <c r="D5">
-        <v>2.587985443786887</v>
+        <v>2.588314648516371</v>
       </c>
       <c r="E5">
-        <v>2.464325615185732</v>
+        <v>2.464380012090376</v>
       </c>
       <c r="F5">
         <v>2.891915246902069</v>
@@ -775,13 +775,13 @@
         <v>34.21770265400227</v>
       </c>
       <c r="C7">
-        <v>47.38557927617373</v>
+        <v>47.40426076711918</v>
       </c>
       <c r="D7">
-        <v>55.13001457750172</v>
+        <v>55.13702739188174</v>
       </c>
       <c r="E7">
-        <v>37.89811079961393</v>
+        <v>37.89894735299254</v>
       </c>
       <c r="F7">
         <v>35.43088110568937</v>
@@ -795,13 +795,13 @@
         <v>14.55499098168092</v>
       </c>
       <c r="C8">
-        <v>9.433217177603751</v>
+        <v>9.43693616899273</v>
       </c>
       <c r="D8">
-        <v>12.53342637469849</v>
+        <v>12.53502068939956</v>
       </c>
       <c r="E8">
-        <v>15.41998126227842</v>
+        <v>15.42032163907164</v>
       </c>
       <c r="F8">
         <v>12.7779465887914</v>
@@ -815,13 +815,13 @@
         <v>14.01709455720877</v>
       </c>
       <c r="C9">
-        <v>3.380036992997976</v>
+        <v>3.381369553060437</v>
       </c>
       <c r="D9">
-        <v>2.951489568007796</v>
+        <v>2.951865012285177</v>
       </c>
       <c r="E9">
-        <v>4.028072901132267</v>
+        <v>4.028161815801722</v>
       </c>
       <c r="F9">
         <v>3.67870286377537</v>
@@ -835,13 +835,13 @@
         <v>6.902093616537502</v>
       </c>
       <c r="C10">
-        <v>30.93311056574766</v>
+        <v>30.94530576592831</v>
       </c>
       <c r="D10">
-        <v>2.77083285595968</v>
+        <v>2.771185319797135</v>
       </c>
       <c r="E10">
-        <v>4.622528968767827</v>
+        <v>4.622631005311204</v>
       </c>
       <c r="F10">
         <v>15.49042402687325</v>
@@ -1025,13 +1025,13 @@
         <v>1659.969061482331</v>
       </c>
       <c r="C9">
-        <v>261.8319631746158</v>
+        <v>259.9351631746158</v>
       </c>
       <c r="D9">
-        <v>3.443301297717567</v>
+        <v>3.429801297717567</v>
       </c>
       <c r="E9">
-        <v>49.86837234875181</v>
+        <v>49.74517234875182</v>
       </c>
       <c r="F9">
         <v>84.74147467732816</v>
@@ -1075,13 +1075,13 @@
         <v>13.37524414060091</v>
       </c>
       <c r="C2">
-        <v>1.140393851878669</v>
+        <v>1.140843445568216</v>
       </c>
       <c r="D2">
-        <v>85.17981900970545</v>
+        <v>85.19065430993561</v>
       </c>
       <c r="E2">
-        <v>98.90465000803484</v>
+        <v>98.9068332044364</v>
       </c>
       <c r="F2">
         <v>19.87225383891903</v>
@@ -1095,13 +1095,13 @@
         <v>9.207133963586177</v>
       </c>
       <c r="C3">
-        <v>0.2224300071798511</v>
+        <v>0.2225176989254961</v>
       </c>
       <c r="D3">
-        <v>3.967054766357532</v>
+        <v>3.9675593956221</v>
       </c>
       <c r="E3">
-        <v>0.04384576266157171</v>
+        <v>0.04384673050192359</v>
       </c>
       <c r="F3">
         <v>5.581796243685438</v>
@@ -1115,13 +1115,13 @@
         <v>15.44283527495152</v>
       </c>
       <c r="C4">
-        <v>0.4261037212244434</v>
+        <v>0.4262717101554951</v>
       </c>
       <c r="D4">
-        <v>0.0697422909281496</v>
+        <v>0.06975116249737492</v>
       </c>
       <c r="E4">
-        <v>0.03606865005067748</v>
+        <v>0.03606944622099904</v>
       </c>
       <c r="F4">
         <v>5.149984079374933</v>
@@ -1135,13 +1135,13 @@
         <v>2.509816797346649</v>
       </c>
       <c r="C5">
-        <v>85.1116318042241</v>
+        <v>85.14518657348492</v>
       </c>
       <c r="D5">
-        <v>0.03700375563083343</v>
+        <v>0.03700846269415622</v>
       </c>
       <c r="E5">
-        <v>0.01046349856429663</v>
+        <v>0.01046372953293574</v>
       </c>
       <c r="F5">
         <v>0.1232507442885361</v>
@@ -1175,13 +1175,13 @@
         <v>9.010385630791047</v>
       </c>
       <c r="C7">
-        <v>7.099597856983993</v>
+        <v>7.102396832434066</v>
       </c>
       <c r="D7">
-        <v>7.463173976218247</v>
+        <v>7.464123329382438</v>
       </c>
       <c r="E7">
-        <v>0.01484703009635742</v>
+        <v>0.01484735782597052</v>
       </c>
       <c r="F7">
         <v>24.0870171383071</v>
@@ -1195,13 +1195,13 @@
         <v>16.54838602243218</v>
       </c>
       <c r="C8">
-        <v>0.5598881450013304</v>
+        <v>0.5601088776687595</v>
       </c>
       <c r="D8">
-        <v>0.03913592783669327</v>
+        <v>0.03914090612301538</v>
       </c>
       <c r="E8">
-        <v>0.09665295033077663</v>
+        <v>0.09665508382372509</v>
       </c>
       <c r="F8">
         <v>1.007917616868353</v>
@@ -1215,13 +1215,13 @@
         <v>31.42479902690015</v>
       </c>
       <c r="C9">
-        <v>5.439954613507614</v>
+        <v>5.40267486176304</v>
       </c>
       <c r="D9">
-        <v>3.244070273323076</v>
+        <v>3.23176243374531</v>
       </c>
       <c r="E9">
-        <v>0.8934721002614577</v>
+        <v>0.8912844476580158</v>
       </c>
       <c r="F9">
         <v>29.36261719867933</v>
@@ -1262,16 +1262,16 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>255.2290121415143</v>
+        <v>255.2290104137513</v>
       </c>
       <c r="C2">
-        <v>27.5319</v>
+        <v>25.6351</v>
       </c>
       <c r="D2">
-        <v>0.1911</v>
+        <v>0.1776</v>
       </c>
       <c r="E2">
-        <v>1.7924</v>
+        <v>1.6692</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>1382.693372264221</v>
+        <v>1382.693373991984</v>
       </c>
       <c r="C8">
         <v>2239.112817161874</v>
@@ -1432,16 +1432,16 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>4.831728854764994</v>
+        <v>4.831728822056791</v>
       </c>
       <c r="C2">
-        <v>0.5720168179915723</v>
+        <v>0.5328179098867949</v>
       </c>
       <c r="D2">
-        <v>0.180042864573883</v>
+        <v>0.1673452653409167</v>
       </c>
       <c r="E2">
-        <v>0.03211372894444833</v>
+        <v>0.02990706293267252</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1455,13 +1455,13 @@
         <v>6.958305291451017</v>
       </c>
       <c r="C3">
-        <v>7.049356398615831</v>
+        <v>7.052135566661121</v>
       </c>
       <c r="D3">
-        <v>27.14060778674271</v>
+        <v>27.14406020818733</v>
       </c>
       <c r="E3">
-        <v>5.312802665263391</v>
+        <v>5.312919938734963</v>
       </c>
       <c r="F3">
         <v>1.119498039890622</v>
@@ -1475,13 +1475,13 @@
         <v>33.16009363682408</v>
       </c>
       <c r="C4">
-        <v>22.03223813999666</v>
+        <v>22.04092422263208</v>
       </c>
       <c r="D4">
-        <v>13.45566460317948</v>
+        <v>13.45737623120906</v>
       </c>
       <c r="E4">
-        <v>32.5580527947014</v>
+        <v>32.55877147298091</v>
       </c>
       <c r="F4">
         <v>28.29858429119465</v>
@@ -1495,13 +1495,13 @@
         <v>18.25106751154952</v>
       </c>
       <c r="C5">
-        <v>17.89900896701185</v>
+        <v>17.90606554791805</v>
       </c>
       <c r="D5">
-        <v>42.0684272181114</v>
+        <v>42.0737785330639</v>
       </c>
       <c r="E5">
-        <v>22.61904828082336</v>
+        <v>22.6195475680137</v>
       </c>
       <c r="F5">
         <v>11.37990078069523</v>
@@ -1515,13 +1515,13 @@
         <v>6.389617112758607</v>
       </c>
       <c r="C6">
-        <v>3.722205980466326</v>
+        <v>3.723673438675834</v>
       </c>
       <c r="D6">
-        <v>7.321838709834978</v>
+        <v>7.322770084444364</v>
       </c>
       <c r="E6">
-        <v>10.97625692598461</v>
+        <v>10.976499213123</v>
       </c>
       <c r="F6">
         <v>3.751310965368355</v>
@@ -1535,13 +1535,13 @@
         <v>4.233482064484347</v>
       </c>
       <c r="C7">
-        <v>2.204222043577008</v>
+        <v>2.205091045386795</v>
       </c>
       <c r="D7">
-        <v>4.853545572752886</v>
+        <v>4.854162968094563</v>
       </c>
       <c r="E7">
-        <v>20.19998233801284</v>
+        <v>20.20042822734917</v>
       </c>
       <c r="F7">
         <v>5.927521457556067</v>
@@ -1552,16 +1552,16 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>26.17570552816744</v>
+        <v>26.17570556087564</v>
       </c>
       <c r="C8">
-        <v>46.52095165234075</v>
+        <v>46.53929226883931</v>
       </c>
       <c r="D8">
-        <v>4.979873244804656</v>
+        <v>4.980506709659863</v>
       </c>
       <c r="E8">
-        <v>8.301743266269957</v>
+        <v>8.301926516865597</v>
       </c>
       <c r="F8">
         <v>49.52318446529506</v>
